--- a/PAIEMENT MOIS MAI PVT LOUMA.xlsx
+++ b/PAIEMENT MOIS MAI PVT LOUMA.xlsx
@@ -9,14 +9,16 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView minimized="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="DETAILS PAIEMENT MAI VTO" sheetId="1" r:id="rId1"/>
     <sheet name="TOTAL PAIEMENT MAI" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -887,14 +889,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -902,7 +898,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -922,6 +924,27 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="DETAILS PAIEMENT JUIN VTO"/>
+      <sheetName val="PAIEMENT PAR PVT"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="E2">
+            <v>33354.15</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1246,10 +1269,10 @@
   <cols>
     <col min="1" max="1" width="15.9140625" customWidth="1"/>
     <col min="2" max="2" width="21.4140625" customWidth="1"/>
-    <col min="3" max="3" width="22.4140625" customWidth="1"/>
+    <col min="3" max="3" width="24.1640625" customWidth="1"/>
     <col min="4" max="4" width="10.9140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5" style="51" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="51" customWidth="1"/>
     <col min="8" max="8" width="8.6640625" style="51" customWidth="1"/>
     <col min="9" max="9" width="11.6640625" style="51" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.08203125" style="51" bestFit="1" customWidth="1"/>
@@ -1270,20 +1293,20 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="69" t="s">
+      <c r="G1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="71"/>
-      <c r="M1" s="72" t="s">
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="74"/>
+      <c r="M1" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
       <c r="R1" s="2"/>
       <c r="S1" s="3" t="s">
         <v>2</v>
@@ -1356,10 +1379,10 @@
       </c>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="71" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="10" t="s">
@@ -1417,8 +1440,8 @@
       <c r="V3" s="11"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="73"/>
-      <c r="B4" s="73"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="71"/>
       <c r="C4" s="10" t="s">
         <v>17</v>
       </c>
@@ -1474,8 +1497,8 @@
       <c r="V4" s="11"/>
     </row>
     <row r="5" spans="1:22">
-      <c r="A5" s="73"/>
-      <c r="B5" s="73"/>
+      <c r="A5" s="71"/>
+      <c r="B5" s="71"/>
       <c r="C5" s="10" t="s">
         <v>20</v>
       </c>
@@ -1531,8 +1554,8 @@
       <c r="V5" s="11"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="73"/>
-      <c r="B6" s="73"/>
+      <c r="A6" s="71"/>
+      <c r="B6" s="71"/>
       <c r="C6" s="10" t="s">
         <v>20</v>
       </c>
@@ -1627,10 +1650,10 @@
       </c>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="69" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="10" t="s">
@@ -1688,8 +1711,8 @@
       <c r="V8" s="11"/>
     </row>
     <row r="9" spans="1:22">
-      <c r="A9" s="74"/>
-      <c r="B9" s="74"/>
+      <c r="A9" s="69"/>
+      <c r="B9" s="69"/>
       <c r="C9" s="10" t="s">
         <v>32</v>
       </c>
@@ -1745,8 +1768,8 @@
       <c r="V9" s="11"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="74"/>
-      <c r="B10" s="74"/>
+      <c r="A10" s="69"/>
+      <c r="B10" s="69"/>
       <c r="C10" s="10" t="s">
         <v>36</v>
       </c>
@@ -1802,8 +1825,8 @@
       <c r="V10" s="11"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="74"/>
-      <c r="B11" s="74"/>
+      <c r="A11" s="69"/>
+      <c r="B11" s="69"/>
       <c r="C11" s="10" t="s">
         <v>40</v>
       </c>
@@ -1898,10 +1921,10 @@
       </c>
     </row>
     <row r="13" spans="1:22">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="69" t="s">
         <v>47</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -1959,8 +1982,8 @@
       <c r="V13" s="11"/>
     </row>
     <row r="14" spans="1:22">
-      <c r="A14" s="74"/>
-      <c r="B14" s="74"/>
+      <c r="A14" s="69"/>
+      <c r="B14" s="69"/>
       <c r="C14" s="10" t="s">
         <v>28</v>
       </c>
@@ -2016,8 +2039,8 @@
       <c r="V14" s="11"/>
     </row>
     <row r="15" spans="1:22">
-      <c r="A15" s="74"/>
-      <c r="B15" s="74"/>
+      <c r="A15" s="69"/>
+      <c r="B15" s="69"/>
       <c r="C15" s="10" t="s">
         <v>55</v>
       </c>
@@ -2073,8 +2096,8 @@
       <c r="V15" s="11"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="74"/>
-      <c r="B16" s="74"/>
+      <c r="A16" s="69"/>
+      <c r="B16" s="69"/>
       <c r="C16" s="10" t="s">
         <v>58</v>
       </c>
@@ -2169,10 +2192,10 @@
       </c>
     </row>
     <row r="18" spans="1:22">
-      <c r="A18" s="74" t="s">
+      <c r="A18" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="74" t="s">
+      <c r="B18" s="69" t="s">
         <v>62</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -2230,8 +2253,8 @@
       <c r="V18" s="11"/>
     </row>
     <row r="19" spans="1:22">
-      <c r="A19" s="74"/>
-      <c r="B19" s="74"/>
+      <c r="A19" s="69"/>
+      <c r="B19" s="69"/>
       <c r="C19" s="10" t="s">
         <v>66</v>
       </c>
@@ -2287,8 +2310,8 @@
       <c r="V19" s="11"/>
     </row>
     <row r="20" spans="1:22">
-      <c r="A20" s="74"/>
-      <c r="B20" s="74"/>
+      <c r="A20" s="69"/>
+      <c r="B20" s="69"/>
       <c r="C20" s="10" t="s">
         <v>69</v>
       </c>
@@ -2344,8 +2367,8 @@
       <c r="V20" s="11"/>
     </row>
     <row r="21" spans="1:22">
-      <c r="A21" s="74"/>
-      <c r="B21" s="74"/>
+      <c r="A21" s="69"/>
+      <c r="B21" s="69"/>
       <c r="C21" s="42" t="s">
         <v>71</v>
       </c>
@@ -2440,10 +2463,10 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="14.5">
-      <c r="A23" s="74" t="s">
+      <c r="A23" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="69" t="s">
         <v>77</v>
       </c>
       <c r="C23" s="10" t="s">
@@ -2501,8 +2524,8 @@
       <c r="V23" s="11"/>
     </row>
     <row r="24" spans="1:22" ht="14.5">
-      <c r="A24" s="74"/>
-      <c r="B24" s="74"/>
+      <c r="A24" s="69"/>
+      <c r="B24" s="69"/>
       <c r="C24" s="10" t="s">
         <v>80</v>
       </c>
@@ -2558,8 +2581,8 @@
       <c r="V24" s="11"/>
     </row>
     <row r="25" spans="1:22" ht="14.5">
-      <c r="A25" s="74"/>
-      <c r="B25" s="74"/>
+      <c r="A25" s="69"/>
+      <c r="B25" s="69"/>
       <c r="C25" s="10" t="s">
         <v>83</v>
       </c>
@@ -2615,8 +2638,8 @@
       <c r="V25" s="11"/>
     </row>
     <row r="26" spans="1:22" ht="14.5">
-      <c r="A26" s="74"/>
-      <c r="B26" s="74"/>
+      <c r="A26" s="69"/>
+      <c r="B26" s="69"/>
       <c r="C26" s="10" t="s">
         <v>86</v>
       </c>
@@ -2711,10 +2734,10 @@
       </c>
     </row>
     <row r="28" spans="1:22">
-      <c r="A28" s="74" t="s">
+      <c r="A28" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="74" t="s">
+      <c r="B28" s="69" t="s">
         <v>92</v>
       </c>
       <c r="C28" s="10" t="s">
@@ -2772,8 +2795,8 @@
       <c r="V28" s="11"/>
     </row>
     <row r="29" spans="1:22">
-      <c r="A29" s="74"/>
-      <c r="B29" s="74"/>
+      <c r="A29" s="69"/>
+      <c r="B29" s="69"/>
       <c r="C29" s="10" t="s">
         <v>96</v>
       </c>
@@ -2829,8 +2852,8 @@
       <c r="V29" s="11"/>
     </row>
     <row r="30" spans="1:22">
-      <c r="A30" s="74"/>
-      <c r="B30" s="74"/>
+      <c r="A30" s="69"/>
+      <c r="B30" s="69"/>
       <c r="C30" s="10" t="s">
         <v>99</v>
       </c>
@@ -2886,8 +2909,8 @@
       <c r="V30" s="11"/>
     </row>
     <row r="31" spans="1:22">
-      <c r="A31" s="74"/>
-      <c r="B31" s="74"/>
+      <c r="A31" s="69"/>
+      <c r="B31" s="69"/>
       <c r="C31" s="10" t="s">
         <v>101</v>
       </c>
@@ -3003,6 +3026,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B11"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="B28:B31"/>
     <mergeCell ref="A13:A16"/>
@@ -3011,12 +3040,6 @@
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="A23:A26"/>
     <mergeCell ref="B23:B26"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3080,12 +3103,12 @@
         <v>554166.66666666674</v>
       </c>
       <c r="D4" s="64">
-        <f>+C4*0.05</f>
-        <v>27708.333333333339</v>
+        <f>'[1]PAIEMENT PAR PVT'!$E$2</f>
+        <v>33354.15</v>
       </c>
       <c r="E4" s="11">
         <f>+D4+C4</f>
-        <v>581875.00000000012</v>
+        <v>587520.81666666677</v>
       </c>
       <c r="F4" s="48">
         <v>773316647</v>
@@ -3214,11 +3237,11 @@
       </c>
       <c r="D10" s="65">
         <f>SUM(D4:D9)</f>
-        <v>184224.98333333334</v>
+        <v>189870.8</v>
       </c>
       <c r="E10" s="65">
         <f>SUM(E4:E9)</f>
-        <v>3868724.65</v>
+        <v>3874370.4666666668</v>
       </c>
       <c r="F10" s="10"/>
     </row>
